--- a/artfynd/A 47701-2024 artfynd.xlsx
+++ b/artfynd/A 47701-2024 artfynd.xlsx
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -4218,7 +4218,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>

--- a/artfynd/A 47701-2024 artfynd.xlsx
+++ b/artfynd/A 47701-2024 artfynd.xlsx
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7047826</v>
+        <v>7047828</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>373</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grentaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacodon septentrionalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476775.850286598</v>
+        <v>476806</v>
       </c>
       <c r="R2" t="n">
-        <v>6671112.136196344</v>
+        <v>6671174</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,21 +752,11 @@
           <t>2013-11-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-11-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +768,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>lönn vid gårdsruin</t>
+          <t>lönn i f d hag-slåtteramark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7047828</v>
+        <v>110626067</v>
       </c>
       <c r="B3" t="n">
-        <v>89812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,29 +814,21 @@
           <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476806.1471157625</v>
+        <v>476810</v>
       </c>
       <c r="R3" t="n">
-        <v>6671174.140748543</v>
+        <v>6671174</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Känd lokal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,74 +883,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>lönn i f d hag-slåtteramark</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7047816</v>
+        <v>119154414</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>373</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grentaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Climacodon septentrionalis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476751.9791680198</v>
+        <v>476798</v>
       </c>
       <c r="R4" t="n">
-        <v>6671277.479090372</v>
+        <v>6671228</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,22 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Känd lokal.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,71 +995,70 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>grov gammal sälg i f d hagmark, nu i vägkant</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7047821</v>
+        <v>7047820</v>
       </c>
       <c r="B5" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6457</v>
+        <v>389</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Läderlappslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Collema nigrescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Huds.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476663.1596640045</v>
+        <v>476663</v>
       </c>
       <c r="R5" t="n">
-        <v>6671260.629337065</v>
+        <v>6671261</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,26 +1088,16 @@
           <t>2013-11-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-11-23</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG5" t="b">
         <v>0</v>
@@ -1152,50 +1122,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7047831</v>
+        <v>7047818</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>392</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476814.261934736</v>
+        <v>476656</v>
       </c>
       <c r="R6" t="n">
-        <v>6671275.09419884</v>
+        <v>6671290</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1225,21 +1199,11 @@
           <t>2013-11-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-11-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1251,7 +1215,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>lönn i f d hag-slåtteramark</t>
+          <t>asp i liten grupp aspar i f d hagmark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1269,15 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7047818</v>
+        <v>7047819</v>
       </c>
       <c r="B7" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1302,26 +1261,17 @@
           <t>Degel.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476655.8680514815</v>
+        <v>476663</v>
       </c>
       <c r="R7" t="n">
-        <v>6671289.533927971</v>
+        <v>6671261</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1351,21 +1301,11 @@
           <t>2013-11-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-11-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1377,7 +1317,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>asp i liten grupp aspar i f d hagmark</t>
+          <t>grov asp i f d hagmark</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1395,15 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7047819</v>
+        <v>110622645</v>
       </c>
       <c r="B8" t="n">
-        <v>78479</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1429,19 +1364,20 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476663.1596640045</v>
+        <v>476657</v>
       </c>
       <c r="R8" t="n">
-        <v>6671260.629337065</v>
+        <v>6671273</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1465,22 +1401,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,74 +1427,65 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>grov asp i f d hagmark</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7047823</v>
+        <v>110627018</v>
       </c>
       <c r="B9" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>392</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476663.1596640045</v>
+        <v>476782</v>
       </c>
       <c r="R9" t="n">
-        <v>6671260.629337065</v>
+        <v>6671424</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,62 +1509,52 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>grov asp i f d hagmark</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7047820</v>
+        <v>110636895</v>
       </c>
       <c r="B10" t="n">
-        <v>78477</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,46 +1562,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Läderlappslav</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Collema nigrescens</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Huds.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476663.1596640045</v>
+        <v>476657</v>
       </c>
       <c r="R10" t="n">
-        <v>6671260.629337065</v>
+        <v>6671288</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,36 +1619,47 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-07-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2 aspar med ett antal små bålar</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>grov asp i f d hagmark</t>
+          <t>lövrik granskog av örttyp</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,22 +1670,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7047830</v>
+        <v>104670139</v>
       </c>
       <c r="B11" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,37 +1688,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Ludvika, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476803.4876077307</v>
+        <v>476743</v>
       </c>
       <c r="R11" t="n">
-        <v>6671226.401800487</v>
+        <v>6670953</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1825,22 +1743,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2022-11-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,74 +1769,65 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>grov asp vid stenmur i f d hagmark</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Niklas Trogen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7047822</v>
+        <v>112024641</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>5754</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476663.1596640045</v>
+        <v>476758</v>
       </c>
       <c r="R12" t="n">
-        <v>6671260.629337065</v>
+        <v>6670970</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,22 +1851,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2013-11-23</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1968,36 +1877,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>grov asp i f d hagmark</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104670139</v>
+        <v>7047822</v>
       </c>
       <c r="B13" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2005,38 +1904,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ludvika, Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476742.946185804</v>
+        <v>476663</v>
       </c>
       <c r="R13" t="n">
-        <v>6670953.614742079</v>
+        <v>6671261</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2060,22 +1958,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-11-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:35</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,31 +1974,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>grov asp i f d hagmark</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110637343</v>
+        <v>7047831</v>
       </c>
       <c r="B14" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,28 +2023,17 @@
           <t>(Dicks.) Nyl.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476793.309069214</v>
+        <v>476814</v>
       </c>
       <c r="R14" t="n">
-        <v>6671193.129556644</v>
+        <v>6671275</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2183,22 +2060,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2207,33 +2074,12 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>lövrik granskog av örttyp</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>60 cm diam</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula # 60 cm diam</t>
+          <t>lönn i f d hag-slåtteramark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2244,22 +2090,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>110626971</v>
+        <v>110626188</v>
       </c>
       <c r="B15" t="n">
-        <v>78467</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2267,35 +2108,35 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476791.2513657651</v>
+        <v>476783</v>
       </c>
       <c r="R15" t="n">
-        <v>6671419.030136611</v>
+        <v>6671201</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2327,7 +2168,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2337,7 +2178,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2364,15 +2205,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>110627007</v>
+        <v>110637045</v>
       </c>
       <c r="B16" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2380,38 +2216,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476782.3127104478</v>
+        <v>476691</v>
       </c>
       <c r="R16" t="n">
-        <v>6671424.062114042</v>
+        <v>6671124</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2438,54 +2276,60 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>lövrik granskog av örttyp</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
+          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>110637045</v>
+        <v>110637091</v>
       </c>
       <c r="B17" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,10 +2364,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476691.1975811766</v>
+        <v>476674</v>
       </c>
       <c r="R17" t="n">
-        <v>6671124.117973056</v>
+        <v>6671080</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2553,19 +2397,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2585,17 +2419,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>skogslönn</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2613,15 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>110637222</v>
+        <v>110637343</v>
       </c>
       <c r="B18" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2629,25 +2458,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2656,10 +2493,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476681.088646533</v>
+        <v>476793</v>
       </c>
       <c r="R18" t="n">
-        <v>6671023.670872978</v>
+        <v>6671193</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2689,19 +2526,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,9 +2556,14 @@
           <t>Populus tremula</t>
         </is>
       </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>60 cm diam</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Populus tremula # 60 cm diam</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2749,15 +2581,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>110625429</v>
+        <v>7047821</v>
       </c>
       <c r="B19" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2765,38 +2592,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476740.3158190299</v>
+        <v>476663</v>
       </c>
       <c r="R19" t="n">
-        <v>6671010.35711132</v>
+        <v>6671261</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2820,22 +2646,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2846,31 +2662,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>grov asp i f d hagmark</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>110636912</v>
+        <v>110626971</v>
       </c>
       <c r="B20" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2878,40 +2694,38 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6457</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476655.2752410838</v>
+        <v>476791</v>
       </c>
       <c r="R20" t="n">
-        <v>6671196.494271322</v>
+        <v>6671419</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2940,7 +2754,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2950,7 +2764,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2959,93 +2773,69 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>lövrik granskog av örttyp</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
+          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>110622645</v>
+        <v>110637424</v>
       </c>
       <c r="B21" t="n">
-        <v>78488</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>392</v>
+        <v>6457</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476657.2616989746</v>
+        <v>476818</v>
       </c>
       <c r="R21" t="n">
-        <v>6671273.603344486</v>
+        <v>6671417</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3072,54 +2862,65 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>09:35</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>lövrik granskog av örttyp</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>grov solitär på f d gård</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Acer platanoides # grov solitär på f d gård</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
+          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>110626188</v>
+        <v>7047816</v>
       </c>
       <c r="B22" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3127,38 +2928,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476782.8936532611</v>
+        <v>476752</v>
       </c>
       <c r="R22" t="n">
-        <v>6671201.156572128</v>
+        <v>6671277</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3182,22 +2982,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:09</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3208,31 +2998,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>grov gammal sälg i f d hagmark, nu i vägkant</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>110637091</v>
+        <v>110624544</v>
       </c>
       <c r="B23" t="n">
-        <v>78512</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,40 +3030,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476673.4690644927</v>
+        <v>476692</v>
       </c>
       <c r="R23" t="n">
-        <v>6671079.448818967</v>
+        <v>6671078</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3302,7 +3090,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3312,7 +3100,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3321,54 +3109,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>lövrik granskog av örttyp</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
+          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>110627069</v>
+        <v>7047823</v>
       </c>
       <c r="B24" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3394,20 +3156,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476722.0227023831</v>
+        <v>476663</v>
       </c>
       <c r="R24" t="n">
-        <v>6671425.937293835</v>
+        <v>6671261</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3431,22 +3192,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:52</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3457,72 +3208,69 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>grov asp i f d hagmark</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>110636895</v>
+        <v>7047826</v>
       </c>
       <c r="B25" t="n">
-        <v>78488</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476656.858434103</v>
+        <v>476776</v>
       </c>
       <c r="R25" t="n">
-        <v>6671288.532513292</v>
+        <v>6671112</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3546,27 +3294,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 aspar med ett antal små bålar</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3575,28 +3308,12 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>lövrik granskog av örttyp</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+          <t>lönn vid gårdsruin</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3607,22 +3324,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>110637220</v>
+        <v>7047830</v>
       </c>
       <c r="B26" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3630,45 +3342,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476681.088646533</v>
+        <v>476803</v>
       </c>
       <c r="R26" t="n">
-        <v>6671023.670872978</v>
+        <v>6671226</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3695,22 +3396,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-11-23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3719,28 +3410,12 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>lövrik granskog av örttyp</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+          <t>grov asp vid stenmur i f d hagmark</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3751,22 +3426,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>110637295</v>
+        <v>110622732</v>
       </c>
       <c r="B27" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3774,40 +3444,38 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476865.6821753727</v>
+        <v>476663</v>
       </c>
       <c r="R27" t="n">
-        <v>6671130.973308329</v>
+        <v>6671187</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3836,7 +3504,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3846,7 +3514,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3855,59 +3523,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>lövrik granskog av örttyp</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>2x25 cm diam</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Acer platanoides # 2x25 cm diam</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
+          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>110624719</v>
+        <v>110625429</v>
       </c>
       <c r="B28" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3915,35 +3552,35 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476685.754683194</v>
+        <v>476740</v>
       </c>
       <c r="R28" t="n">
-        <v>6671052.003592911</v>
+        <v>6671011</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3975,7 +3612,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3985,7 +3622,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4012,15 +3649,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>110622732</v>
+        <v>110627007</v>
       </c>
       <c r="B29" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4049,14 +3681,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476663.1858426144</v>
+        <v>476782</v>
       </c>
       <c r="R29" t="n">
-        <v>6671186.492568373</v>
+        <v>6671424</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -4088,7 +3720,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4098,7 +3730,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4125,51 +3757,46 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>110627018</v>
+        <v>110627069</v>
       </c>
       <c r="B30" t="n">
-        <v>78488</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>392</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476782.3127104478</v>
+        <v>476722</v>
       </c>
       <c r="R30" t="n">
-        <v>6671424.062114042</v>
+        <v>6671426</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4218,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="b">
         <v>0</v>
@@ -4238,15 +3865,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>110637424</v>
+        <v>110636912</v>
       </c>
       <c r="B31" t="n">
-        <v>78467</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4254,21 +3876,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6457</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4281,10 +3903,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476818.15247657</v>
+        <v>476655</v>
       </c>
       <c r="R31" t="n">
-        <v>6671417.367214552</v>
+        <v>6671196</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4314,19 +3936,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4354,14 +3966,9 @@
           <t>Acer platanoides</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>grov solitär på f d gård</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Acer platanoides # grov solitär på f d gård</t>
+          <t>Acer platanoides</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4382,12 +3989,7 @@
         <v>110637026</v>
       </c>
       <c r="B32" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4422,10 +4024,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476660.4721077504</v>
+        <v>476661</v>
       </c>
       <c r="R32" t="n">
-        <v>6671151.680061737</v>
+        <v>6671151</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4455,19 +4057,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4515,15 +4107,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>110624544</v>
+        <v>110637125</v>
       </c>
       <c r="B33" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4531,38 +4118,40 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476691.4016029366</v>
+        <v>476674</v>
       </c>
       <c r="R33" t="n">
-        <v>6671077.84195652</v>
+        <v>6671080</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4589,54 +4178,60 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>lövrik granskog av örttyp</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
+          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>110637137</v>
+        <v>110637222</v>
       </c>
       <c r="B34" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4644,33 +4239,25 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
@@ -4679,10 +4266,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476673.4690644927</v>
+        <v>476681</v>
       </c>
       <c r="R34" t="n">
-        <v>6671079.448818967</v>
+        <v>6671024</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4712,19 +4299,9 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2023-07-06</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4752,14 +4329,9 @@
           <t>Populus tremula</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>80 cm diam</t>
-        </is>
-      </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Populus tremula # 80 cm diam</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4777,15 +4349,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>110637125</v>
+        <v>110624719</v>
       </c>
       <c r="B35" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4793,40 +4360,38 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lönnhöjden, Dlr</t>
+          <t>Lönnhöjden, Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476673.4690644927</v>
+        <v>476686</v>
       </c>
       <c r="R35" t="n">
-        <v>6671079.448818967</v>
+        <v>6671052</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4855,7 +4420,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4865,7 +4430,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4874,93 +4439,77 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>lövrik granskog av örttyp</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>skogslönn</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Acer platanoides</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
+          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>110626067</v>
+        <v>110637137</v>
       </c>
       <c r="B36" t="n">
-        <v>89825</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>373</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grentaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Climacodon septentrionalis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476810.1278328588</v>
+        <v>476674</v>
       </c>
       <c r="R36" t="n">
-        <v>6671173.120416338</v>
+        <v>6671080</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4987,98 +4536,114 @@
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2023-07-06</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Känd lokal</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>lövrik granskog av örttyp</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>80 cm diam</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Populus tremula # 80 cm diam</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Andreas Öster, Janolof Hermansson, Niklas Trogen</t>
+          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112024641</v>
+        <v>110637220</v>
       </c>
       <c r="B37" t="n">
-        <v>89115</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5754</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476758</v>
+        <v>476681</v>
       </c>
       <c r="R37" t="n">
-        <v>6670971</v>
+        <v>6671024</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5102,22 +4667,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:24</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5126,71 +4681,90 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>lövrik granskog av örttyp</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119154414</v>
+        <v>110637295</v>
       </c>
       <c r="B38" t="n">
-        <v>90987</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>373</v>
+        <v>229497</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grentaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Climacodon septentrionalis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lönnhöjden (Lönnhöjden), Dlr</t>
+          <t>Lönnhöjden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476798</v>
+        <v>476866</v>
       </c>
       <c r="R38" t="n">
-        <v>6671228</v>
+        <v>6671131</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5214,27 +4788,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Känd lokal.</t>
+          <t>2023-07-06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5243,18 +4802,44 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>lövrik granskog av örttyp</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>skogslönn</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Acer platanoides</t>
+        </is>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>2x25 cm diam</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Acer platanoides # 2x25 cm diam</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson, Andreas Öster, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
